--- a/data/trans_orig/P59-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P59-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2007</t>
+          <t>Población según su estado civil en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>63713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98100</t>
+          <t>99291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>307439</t>
+          <t>308507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371618</t>
+          <t>372824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380856</t>
+          <t>382007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455987</t>
+          <t>457440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>36608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48549</t>
+          <t>50061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41307</t>
+          <t>40481</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>70633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178557</t>
+          <t>178737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232253</t>
+          <t>232395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106984</t>
+          <t>106371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146744</t>
+          <t>149521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299927</t>
+          <t>301388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369162</t>
+          <t>369489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688204</t>
+          <t>688102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>747209</t>
+          <t>749251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>765377</t>
+          <t>761825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>835566</t>
+          <t>835137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1469632</t>
+          <t>1468441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1563568</t>
+          <t>1562655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64228</t>
+          <t>65876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>61399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>96356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53123</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47901</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>55320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91570</t>
+          <t>91327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>645096</t>
+          <t>642313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>727494</t>
+          <t>727979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>493925</t>
+          <t>493144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>565569</t>
+          <t>568058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1153712</t>
+          <t>1161022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1265134</t>
+          <t>1270230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>887323</t>
+          <t>887746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>971986</t>
+          <t>972378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>889201</t>
+          <t>884405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>966657</t>
+          <t>965084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801405</t>
+          <t>1801578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917511</t>
+          <t>1914576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195910</t>
+          <t>195148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241318</t>
+          <t>241507</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167635</t>
+          <t>165713</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>209342</t>
+          <t>210699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>373146</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>438402</t>
+          <t>436512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295991</t>
+          <t>295564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343286</t>
+          <t>342832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228144</t>
+          <t>225169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270802</t>
+          <t>270310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535420</t>
+          <t>538834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>602397</t>
+          <t>599685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133988</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>362549</t>
+          <t>367027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439107</t>
+          <t>440046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>472570</t>
+          <t>469086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559832</t>
+          <t>554923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52716</t>
+          <t>54494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81172</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84068</t>
+          <t>81995</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>124483</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67183</t>
+          <t>69113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>76620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122957</t>
+          <t>121879</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1053848</t>
+          <t>1048221</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1162057</t>
+          <t>1164703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>796621</t>
+          <t>795026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>897720</t>
+          <t>893177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1881452</t>
+          <t>1880338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2025830</t>
+          <t>2024984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1911947</t>
+          <t>1910809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2025711</t>
+          <t>2025562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1916096</t>
+          <t>1914300</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2030039</t>
+          <t>2030841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3857973</t>
+          <t>3863305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4021642</t>
+          <t>4016350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2012</t>
+          <t>Población según su estado civil en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>73765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111936</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>320539</t>
+          <t>320461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>387127</t>
+          <t>384786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>407488</t>
+          <t>410784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>484648</t>
+          <t>487730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>25583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27810</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>54071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37665</t>
+          <t>38875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>27950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>54267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169241</t>
+          <t>167347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>217256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91760</t>
+          <t>92012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133820</t>
+          <t>132642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273425</t>
+          <t>269719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>339451</t>
+          <t>337421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632424</t>
+          <t>630862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>689617</t>
+          <t>691010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>788193</t>
+          <t>788069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>860360</t>
+          <t>860169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1436525</t>
+          <t>1438311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1529080</t>
+          <t>1529024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37321</t>
+          <t>36925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49268</t>
+          <t>47663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>80711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>68367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108829</t>
+          <t>109623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76060</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60081</t>
+          <t>58422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112659</t>
+          <t>111449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159699</t>
+          <t>158417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50865</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67118</t>
+          <t>66303</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68814</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>104538</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>715994</t>
+          <t>715709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>802218</t>
+          <t>804379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510974</t>
+          <t>507718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>587305</t>
+          <t>587142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1244540</t>
+          <t>1244176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1365048</t>
+          <t>1367965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040659</t>
+          <t>1039219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129411</t>
+          <t>1127880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973801</t>
+          <t>979212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058098</t>
+          <t>1062972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2038006</t>
+          <t>2043878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2167208</t>
+          <t>2169163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43251</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175049</t>
+          <t>172819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>218123</t>
+          <t>217669</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153880</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>196411</t>
+          <t>196952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336524</t>
+          <t>337835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>399649</t>
+          <t>402660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241203</t>
+          <t>239724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284298</t>
+          <t>285068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231543</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275274</t>
+          <t>276562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488074</t>
+          <t>485566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551243</t>
+          <t>551476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100326</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145959</t>
+          <t>147400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>387455</t>
+          <t>389155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>464521</t>
+          <t>465301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>499922</t>
+          <t>504160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>596134</t>
+          <t>592658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64444</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104990</t>
+          <t>107428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96758</t>
+          <t>96441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142928</t>
+          <t>140223</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172723</t>
+          <t>173254</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230735</t>
+          <t>232688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61683</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99827</t>
+          <t>99378</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>110784</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>160110</t>
+          <t>161185</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1088662</t>
+          <t>1087132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1205643</t>
+          <t>1201340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>782874</t>
+          <t>777400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>886986</t>
+          <t>884486</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1905102</t>
+          <t>1904048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2055841</t>
+          <t>2058080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1946660</t>
+          <t>1949209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2065656</t>
+          <t>2065861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2033045</t>
+          <t>2037846</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2154437</t>
+          <t>2159119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4024343</t>
+          <t>4026164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4192000</t>
+          <t>4193608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2016</t>
+          <t>Población según su estado civil en 2016 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83538</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116239</t>
+          <t>119079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>271989</t>
+          <t>270938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>332446</t>
+          <t>329972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>363494</t>
+          <t>362558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>437495</t>
+          <t>432366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>40692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54864</t>
+          <t>53661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118854</t>
+          <t>117958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161370</t>
+          <t>159268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96616</t>
+          <t>93499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187485</t>
+          <t>187753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242944</t>
+          <t>241971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456365</t>
+          <t>456405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507912</t>
+          <t>507473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>542939</t>
+          <t>544845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609829</t>
+          <t>608262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1019485</t>
+          <t>1018465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1100099</t>
+          <t>1102246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44587</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135703</t>
+          <t>133718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117835</t>
+          <t>118124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166170</t>
+          <t>167071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51635</t>
+          <t>53589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>87831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86059</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127222</t>
+          <t>125520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146113</t>
+          <t>146861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203724</t>
+          <t>201311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75509</t>
+          <t>72263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,47 +7574,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>72153</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>56606</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>87959</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>72153</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>54453</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>90233</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108452</t>
+          <t>108674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152634</t>
+          <t>152528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755896</t>
+          <t>759014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>844747</t>
+          <t>845376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604557</t>
+          <t>604538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>689279</t>
+          <t>688486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1381653</t>
+          <t>1381322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1502530</t>
+          <t>1508236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1068839</t>
+          <t>1074088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1160471</t>
+          <t>1162885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010640</t>
+          <t>1007726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1099863</t>
+          <t>1096393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2103636</t>
+          <t>2107818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2233731</t>
+          <t>2231876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39854</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51296</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>48167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>188343</t>
+          <t>190717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236199</t>
+          <t>238480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>175189</t>
+          <t>174265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>220149</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>378218</t>
+          <t>382831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>443716</t>
+          <t>445014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267091</t>
+          <t>269130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317478</t>
+          <t>318204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255575</t>
+          <t>260097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304621</t>
+          <t>307574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541449</t>
+          <t>536945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609623</t>
+          <t>604670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121203</t>
+          <t>123459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168213</t>
+          <t>167479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>395249</t>
+          <t>393858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>479536</t>
+          <t>477092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>532235</t>
+          <t>528423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>631703</t>
+          <t>626163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113130</t>
+          <t>109564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136469</t>
+          <t>138139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185287</t>
+          <t>187255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216737</t>
+          <t>214349</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283761</t>
+          <t>283178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78116</t>
+          <t>78766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118270</t>
+          <t>118237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83728</t>
+          <t>84525</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124799</t>
+          <t>124793</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>174782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>229392</t>
+          <t>230188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1096932</t>
+          <t>1101498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1211832</t>
+          <t>1210863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>863559</t>
+          <t>864973</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>971348</t>
+          <t>968873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1998980</t>
+          <t>1997495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2149919</t>
+          <t>2151418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1835303</t>
+          <t>1834936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1955923</t>
+          <t>1953073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1844892</t>
+          <t>1848717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1971014</t>
+          <t>1975760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3729319</t>
+          <t>3717912</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3888878</t>
+          <t>3895653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su estado civil en 2023</t>
+          <t>Población según su estado civil en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64016</t>
+          <t>64589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281377</t>
+          <t>280466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321451</t>
+          <t>321998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>350920</t>
+          <t>352520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401239</t>
+          <t>404567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45697</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>65929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33291</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98686</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139759</t>
+          <t>139965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52731</t>
+          <t>52886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81718</t>
+          <t>80943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158264</t>
+          <t>158647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209120</t>
+          <t>207802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>260528</t>
+          <t>260489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304166</t>
+          <t>304606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320318</t>
+          <t>320787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362529</t>
+          <t>363277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595653</t>
+          <t>593615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>654909</t>
+          <t>655096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>69963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103590</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164958</t>
+          <t>160009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156028</t>
+          <t>154523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223211</t>
+          <t>224595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>56800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108371</t>
+          <t>108148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92981</t>
+          <t>88567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152361</t>
+          <t>151382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171209</t>
+          <t>167757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245894</t>
+          <t>248798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84179</t>
+          <t>85407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>54098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95918</t>
+          <t>95397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111074</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>165704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>637998</t>
+          <t>586181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1026483</t>
+          <t>1022660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>468623</t>
+          <t>502838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>801357</t>
+          <t>803691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1256876</t>
+          <t>1258025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1746101</t>
+          <t>1756928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1031445</t>
+          <t>1035812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1501874</t>
+          <t>1573500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1087280</t>
+          <t>1092485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1505533</t>
+          <t>1483174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,17 +10809,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2414707</t>
+          <t>2414706</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2188769</t>
+          <t>2181725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2822056</t>
+          <t>2825569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53428</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84655</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>30266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49176</t>
+          <t>48770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75977</t>
+          <t>77096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,47 +11250,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>30412</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>22410</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>40077</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>30412</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>22815</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>40355</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209921</t>
+          <t>210578</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>267392</t>
+          <t>268259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>217723</t>
+          <t>218311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>263830</t>
+          <t>264011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>440421</t>
+          <t>444304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>510550</t>
+          <t>513724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323418</t>
+          <t>324228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>381339</t>
+          <t>382556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>305076</t>
+          <t>304628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>350152</t>
+          <t>348570</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648954</t>
+          <t>642818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>718069</t>
+          <t>715341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120836</t>
+          <t>120838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>189148</t>
+          <t>186524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>393385</t>
+          <t>363761</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>511222</t>
+          <t>509186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>543191</t>
+          <t>549027</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>682696</t>
+          <t>683263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100283</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156535</t>
+          <t>154731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154757</t>
+          <t>156479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>219633</t>
+          <t>220411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274070</t>
+          <t>273959</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>359170</t>
+          <t>360779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68283</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109435</t>
+          <t>110220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96201</t>
+          <t>96020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141551</t>
+          <t>141677</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>175352</t>
+          <t>172020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239433</t>
+          <t>235503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>998560</t>
+          <t>968541</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1370259</t>
+          <t>1367240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>816691</t>
+          <t>824963</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1119540</t>
+          <t>1119397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1955287</t>
+          <t>1911071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2411671</t>
+          <t>2401028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1676959</t>
+          <t>1676489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2156772</t>
+          <t>2177225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1751839</t>
+          <t>1758979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2217946</t>
+          <t>2240420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3484269</t>
+          <t>3488854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4131795</t>
+          <t>4169610</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P59-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63713</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99291</t>
+          <t>97870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308507</t>
+          <t>309203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>372824</t>
+          <t>372814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382007</t>
+          <t>381660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>457440</t>
+          <t>455540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50061</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40481</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70633</t>
+          <t>71431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178737</t>
+          <t>181642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232395</t>
+          <t>230444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106371</t>
+          <t>109505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149521</t>
+          <t>148941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301388</t>
+          <t>303030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369489</t>
+          <t>368422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688102</t>
+          <t>686472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>749251</t>
+          <t>746218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>761825</t>
+          <t>763222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>835137</t>
+          <t>832434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1468441</t>
+          <t>1466807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1562655</t>
+          <t>1563546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65876</t>
+          <t>66056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61399</t>
+          <t>61426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96356</t>
+          <t>96419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50527</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79082</t>
+          <t>79387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>39730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32521</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59393</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91327</t>
+          <t>91409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>642313</t>
+          <t>644939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>727979</t>
+          <t>725643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>493144</t>
+          <t>492156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>568058</t>
+          <t>563595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1161022</t>
+          <t>1157146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1270230</t>
+          <t>1263810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>887746</t>
+          <t>888759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>972378</t>
+          <t>971346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884405</t>
+          <t>890238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965084</t>
+          <t>965671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801578</t>
+          <t>1802622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914576</t>
+          <t>1915465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,47 +2112,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11362</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20718</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11362</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6284</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19382</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195148</t>
+          <t>192504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241507</t>
+          <t>240731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165713</t>
+          <t>166446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>210699</t>
+          <t>210192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>375643</t>
+          <t>378242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>436512</t>
+          <t>441201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295564</t>
+          <t>296803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>342832</t>
+          <t>342318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225169</t>
+          <t>227353</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270310</t>
+          <t>271038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538834</t>
+          <t>534398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599685</t>
+          <t>597134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>93650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136516</t>
+          <t>133706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367027</t>
+          <t>361074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>440046</t>
+          <t>437535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>469086</t>
+          <t>471600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>554923</t>
+          <t>557094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54494</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49178</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82105</t>
+          <t>82927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81995</t>
+          <t>83819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>124483</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69113</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>117458</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121879</t>
+          <t>122368</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>171463</t>
+          <t>173471</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1048221</t>
+          <t>1050023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1164703</t>
+          <t>1163404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>795026</t>
+          <t>789913</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>893177</t>
+          <t>893147</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1880338</t>
+          <t>1878243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2024984</t>
+          <t>2030667</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1910809</t>
+          <t>1914670</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2025562</t>
+          <t>2030554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1914300</t>
+          <t>1920306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2030841</t>
+          <t>2035290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3863305</t>
+          <t>3856515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4016350</t>
+          <t>4019304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>73755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112306</t>
+          <t>112150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>320461</t>
+          <t>325824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>384786</t>
+          <t>389160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>410784</t>
+          <t>409522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>487730</t>
+          <t>485802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>36257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26630</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54071</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>55003</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167347</t>
+          <t>168685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217256</t>
+          <t>218854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92012</t>
+          <t>91057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>130853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269719</t>
+          <t>272312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337421</t>
+          <t>339606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630862</t>
+          <t>629789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>691010</t>
+          <t>689120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>788069</t>
+          <t>786566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>860169</t>
+          <t>859602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1438311</t>
+          <t>1433841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1529024</t>
+          <t>1532103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>37148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80711</t>
+          <t>79431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68367</t>
+          <t>68691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>107842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>74888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58422</t>
+          <t>59577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92856</t>
+          <t>93719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111449</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158417</t>
+          <t>159972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49178</t>
+          <t>51543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>37138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66303</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68857</t>
+          <t>68858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104538</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>715709</t>
+          <t>712694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>804379</t>
+          <t>802460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>507718</t>
+          <t>510370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>587142</t>
+          <t>587954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1244176</t>
+          <t>1247966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1367965</t>
+          <t>1361765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1039219</t>
+          <t>1040390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1127880</t>
+          <t>1127751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979212</t>
+          <t>976466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1062972</t>
+          <t>1060261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2043878</t>
+          <t>2041650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2169163</t>
+          <t>2164632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,82 +5184,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>16982</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9132</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>27056</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>17133</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>41297</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16982</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10066</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>27541</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>27056</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>17055</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>42130</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172819</t>
+          <t>168546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217669</t>
+          <t>215589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153384</t>
+          <t>153794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>196952</t>
+          <t>199226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>341057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>402660</t>
+          <t>400953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239724</t>
+          <t>242531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285068</t>
+          <t>287548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231439</t>
+          <t>230825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276562</t>
+          <t>277872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485566</t>
+          <t>487404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551476</t>
+          <t>551852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101393</t>
+          <t>101356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147400</t>
+          <t>144087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>389155</t>
+          <t>388379</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>465301</t>
+          <t>464628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>504160</t>
+          <t>502105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>592658</t>
+          <t>595925</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67008</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107428</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96441</t>
+          <t>96528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140223</t>
+          <t>140541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>173254</t>
+          <t>171956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232688</t>
+          <t>229542</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>40367</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99378</t>
+          <t>98082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>111743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>161185</t>
+          <t>158173</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1087132</t>
+          <t>1086432</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1201340</t>
+          <t>1202589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>777400</t>
+          <t>787113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>884486</t>
+          <t>888236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1904048</t>
+          <t>1888728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2058080</t>
+          <t>2050957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1949209</t>
+          <t>1948771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2065861</t>
+          <t>2068738</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2037846</t>
+          <t>2040350</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2159119</t>
+          <t>2158834</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4026164</t>
+          <t>4022351</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4193608</t>
+          <t>4194604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>82048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119079</t>
+          <t>117548</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>270938</t>
+          <t>268326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>329972</t>
+          <t>332007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>362558</t>
+          <t>362393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>432366</t>
+          <t>434033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53661</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>27760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>50494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117958</t>
+          <t>119559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159268</t>
+          <t>160226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93499</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187753</t>
+          <t>187666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456405</t>
+          <t>454313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507473</t>
+          <t>506693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>544845</t>
+          <t>545650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608262</t>
+          <t>611758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018465</t>
+          <t>1019265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1102246</t>
+          <t>1101534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44740</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>89395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133718</t>
+          <t>135485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118124</t>
+          <t>117766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167071</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53589</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87831</t>
+          <t>86879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84857</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125520</t>
+          <t>127177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146861</t>
+          <t>149433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201311</t>
+          <t>204451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>43821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>73206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>56539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87959</t>
+          <t>91114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108674</t>
+          <t>108574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152528</t>
+          <t>152335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>759014</t>
+          <t>751889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>845376</t>
+          <t>850153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604538</t>
+          <t>605374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>688486</t>
+          <t>693496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1381322</t>
+          <t>1384418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1508236</t>
+          <t>1510935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1074088</t>
+          <t>1074075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1162885</t>
+          <t>1165753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007726</t>
+          <t>1008357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1096393</t>
+          <t>1101194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2107818</t>
+          <t>2105672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2231876</t>
+          <t>2239441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>55712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41370</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52184</t>
+          <t>50770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48167</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190717</t>
+          <t>191176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238480</t>
+          <t>238375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174265</t>
+          <t>175956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>220269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>382831</t>
+          <t>379590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>445014</t>
+          <t>446381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269130</t>
+          <t>266298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318204</t>
+          <t>316531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260097</t>
+          <t>258158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>305275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536945</t>
+          <t>533392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>604670</t>
+          <t>606916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123459</t>
+          <t>121884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167479</t>
+          <t>168495</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>393858</t>
+          <t>393792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>477092</t>
+          <t>475939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>528423</t>
+          <t>531971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>626163</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70336</t>
+          <t>70076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109564</t>
+          <t>111341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138139</t>
+          <t>136602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187255</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>214349</t>
+          <t>219573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283178</t>
+          <t>281649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78766</t>
+          <t>76659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>117945</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84525</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124793</t>
+          <t>124117</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>174782</t>
+          <t>172640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>230188</t>
+          <t>227762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1101498</t>
+          <t>1097499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1210863</t>
+          <t>1210897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>864973</t>
+          <t>863036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>968873</t>
+          <t>969839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1997495</t>
+          <t>1991574</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2151418</t>
+          <t>2148698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1834936</t>
+          <t>1835216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1953073</t>
+          <t>1953119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1848717</t>
+          <t>1849456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1975760</t>
+          <t>1970541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3717912</t>
+          <t>3720377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3895653</t>
+          <t>3892483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76812</t>
+          <t>81253</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64589</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90248</t>
+          <t>97001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>299876</t>
+          <t>321345</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280466</t>
+          <t>301237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321998</t>
+          <t>344690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>376688</t>
+          <t>402598</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352520</t>
+          <t>376573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404567</t>
+          <t>433337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47402</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65929</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,17 +9901,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>137567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>117788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139965</t>
+          <t>163894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65361</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>57816</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80943</t>
+          <t>88517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>182102</t>
+          <t>209091</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158647</t>
+          <t>181952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207802</t>
+          <t>239233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>283649</t>
+          <t>320207</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>260489</t>
+          <t>292813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304606</t>
+          <t>342253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>341586</t>
+          <t>379055</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320787</t>
+          <t>354849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363277</t>
+          <t>398995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>625234</t>
+          <t>699262</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>593615</t>
+          <t>666308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655096</t>
+          <t>732027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>512281</t>
+          <t>575503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>512281</t>
+          <t>575503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512281</t>
+          <t>575503</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>754363</t>
+          <t>820773</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>754363</t>
+          <t>820773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>754363</t>
+          <t>820773</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1266643</t>
+          <t>1396276</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1266643</t>
+          <t>1396276</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1266643</t>
+          <t>1396276</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>59521</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69963</t>
+          <t>75667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138280</t>
+          <t>155329</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100180</t>
+          <t>136601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160009</t>
+          <t>175185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>194112</t>
+          <t>214851</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154523</t>
+          <t>194270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224595</t>
+          <t>239015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>78180</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108148</t>
+          <t>114758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126419</t>
+          <t>138980</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88567</t>
+          <t>121764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151382</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>212693</t>
+          <t>235591</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167757</t>
+          <t>208726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248798</t>
+          <t>263898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65394</t>
+          <t>72061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45506</t>
+          <t>56984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85407</t>
+          <t>88864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75580</t>
+          <t>85558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54098</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95397</t>
+          <t>102555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>140974</t>
+          <t>157619</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>135106</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165704</t>
+          <t>181676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>895139</t>
+          <t>942442</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>586181</t>
+          <t>885405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1022660</t>
+          <t>999322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>663764</t>
+          <t>679857</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>502838</t>
+          <t>636271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>803691</t>
+          <t>725168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1558903</t>
+          <t>1622299</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1258025</t>
+          <t>1551765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1756928</t>
+          <t>1693853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1186063</t>
+          <t>1057967</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1035812</t>
+          <t>1002859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1573500</t>
+          <t>1109264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1228644</t>
+          <t>1105669</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1092485</t>
+          <t>1060772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1483174</t>
+          <t>1148207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2414706</t>
+          <t>2163636</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2181725</t>
+          <t>2101031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2825569</t>
+          <t>2229987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288702</t>
+          <t>2228603</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288702</t>
+          <t>2228603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288702</t>
+          <t>2228603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2232686</t>
+          <t>2165393</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2232686</t>
+          <t>2165393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2232686</t>
+          <t>2165393</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4521388</t>
+          <t>4393996</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4521388</t>
+          <t>4393996</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4521388</t>
+          <t>4393996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51671</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82402</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32369</t>
+          <t>34045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48770</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50594</t>
+          <t>56289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77096</t>
+          <t>84291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>236711</t>
+          <t>261622</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210578</t>
+          <t>232080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>268259</t>
+          <t>292243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>240086</t>
+          <t>257164</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218311</t>
+          <t>231633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>264011</t>
+          <t>284116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>476797</t>
+          <t>518785</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>444304</t>
+          <t>480697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>513724</t>
+          <t>556906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>354124</t>
+          <t>396896</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324228</t>
+          <t>367784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>382556</t>
+          <t>425931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>327451</t>
+          <t>369865</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>304628</t>
+          <t>342897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348570</t>
+          <t>393792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>681575</t>
+          <t>766762</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>730710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>715341</t>
+          <t>802960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>644312</t>
+          <t>709341</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644312</t>
+          <t>709341</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>644312</t>
+          <t>709341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>657817</t>
+          <t>731425</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>657817</t>
+          <t>731425</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>657817</t>
+          <t>731425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1302129</t>
+          <t>1440766</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1302129</t>
+          <t>1440766</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1302129</t>
+          <t>1440766</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>155478</t>
+          <t>157157</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120838</t>
+          <t>137979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186524</t>
+          <t>180269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>466992</t>
+          <t>510657</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>476563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509186</t>
+          <t>544361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>667814</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>549027</t>
+          <t>630913</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>683263</t>
+          <t>707997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>141615</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>120937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154731</t>
+          <t>165258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>191177</t>
+          <t>208329</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>156479</t>
+          <t>185680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>220411</t>
+          <t>229599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>349944</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>273959</t>
+          <t>321667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>360779</t>
+          <t>382415</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>97973</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66845</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110220</t>
+          <t>119094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119806</t>
+          <t>135470</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96020</t>
+          <t>117971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>208088</t>
+          <t>233444</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>205836</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>235503</t>
+          <t>259370</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1248591</t>
+          <t>1341631</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>968541</t>
+          <t>1266378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1367240</t>
+          <t>1405298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>969211</t>
+          <t>1008545</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>824963</t>
+          <t>954113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1119397</t>
+          <t>1068774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2217802</t>
+          <t>2350175</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1911071</t>
+          <t>2268342</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2401028</t>
+          <t>2449516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1823836</t>
+          <t>1775071</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1676489</t>
+          <t>1712330</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2177225</t>
+          <t>1843468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1897680</t>
+          <t>1854589</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1758979</t>
+          <t>1796456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2240420</t>
+          <t>1904622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3721517</t>
+          <t>3629660</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3488854</t>
+          <t>3536013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4169610</t>
+          <t>3712748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3445294</t>
+          <t>3513447</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3445294</t>
+          <t>3513447</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3445294</t>
+          <t>3513447</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3644866</t>
+          <t>3717591</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3644866</t>
+          <t>3717591</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3644866</t>
+          <t>3717591</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7090161</t>
+          <t>7231037</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7090161</t>
+          <t>7231037</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7090161</t>
+          <t>7231037</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
